--- a/medical_surveys_questionnaires/012_cardiovascular_knowledge_assessment--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/012_cardiovascular_knowledge_assessment--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_120/80_mmhg',_'value':_'normal'}</t>
+          <t>less_than_120/80_mmhg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 120/80 mmHg', 'value': 'normal'}</t>
+          <t>Less than 120/80 mmHg</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'130/90_mmhg',_'value':_'pre_htn'}</t>
+          <t>130/90_mmhg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '130/90 mmHg', 'value': 'pre_htn'}</t>
+          <t>130/90 mmHg</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'140/90_mmhg',_'value':_'stage1'}</t>
+          <t>140/90_mmhg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '140/90 mmHg', 'value': 'stage1'}</t>
+          <t>140/90 mmHg</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'150/100_mmhg',_'value':_'stage2'}</t>
+          <t>150/100_mmhg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '150/100 mmHg', 'value': 'stage2'}</t>
+          <t>150/100 mmHg</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'chest_pain_or_pressure',_'value':_'chest_pain'}</t>
+          <t>chest_pain_or_pressure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Chest pain or pressure', 'value': 'chest_pain'}</t>
+          <t>Chest pain or pressure</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'shortness_of_breath',_'value':_'sob'}</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Shortness of breath', 'value': 'sob'}</t>
+          <t>Shortness of breath</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'nausea_or_lightheadedness',_'value':_'nausea'}</t>
+          <t>nausea_or_lightheadedness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Nausea or lightheadedness', 'value': 'nausea'}</t>
+          <t>Nausea or lightheadedness</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'pain_in_jaw,_neck,_or_back',_'value':_'pain_jaw'}</t>
+          <t>pain_in_jaw,_neck,_or_back</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Pain in jaw, neck, or back', 'value': 'pain_jaw'}</t>
+          <t>Pain in jaw, neck, or back</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'decreased_heart_efficiency',_'value':_'decrease_efficiency'}</t>
+          <t>decreased_heart_efficiency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Decreased heart efficiency', 'value': 'decrease_efficiency'}</t>
+          <t>Decreased heart efficiency</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'lowered_resting_heart_rate',_'value':_'lower_rhr'}</t>
+          <t>lowered_resting_heart_rate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Lowered resting heart rate', 'value': 'lower_rhr'}</t>
+          <t>Lowered resting heart rate</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'increased_ldl_cholesterol',_'value':_'inc_ldl'}</t>
+          <t>increased_ldl_cholesterol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Increased LDL cholesterol', 'value': 'inc_ldl'}</t>
+          <t>Increased LDL cholesterol</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'decreased_lung_capacity',_'value':_'dec_lung'}</t>
+          <t>decreased_lung_capacity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Decreased lung capacity', 'value': 'dec_lung'}</t>
+          <t>Decreased lung capacity</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'high_saturated_fat_diet',_'value':_'high_fat'}</t>
+          <t>high_saturated_fat_diet</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'High saturated fat diet', 'value': 'high_fat'}</t>
+          <t>High saturated fat diet</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'regular_physical_activity',_'value':_'physical_activity'}</t>
+          <t>regular_physical_activity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Regular physical activity', 'value': 'physical_activity'}</t>
+          <t>Regular physical activity</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'chronic_stress',_'value':_'stress'}</t>
+          <t>chronic_stress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Chronic stress', 'value': 'stress'}</t>
+          <t>Chronic stress</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'tobacco_use',_'value':_'tobacco'}</t>
+          <t>tobacco_use</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Tobacco use', 'value': 'tobacco'}</t>
+          <t>Tobacco use</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'heart-healthy_nutrition',_'value':_'nutrition'}</t>
+          <t>heart-healthy_nutrition</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Heart-Healthy Nutrition', 'value': 'nutrition'}</t>
+          <t>Heart-Healthy Nutrition</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'stress_management',_'value':_'stress_mgmt'}</t>
+          <t>stress_management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Stress Management', 'value': 'stress_mgmt'}</t>
+          <t>Stress Management</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'blood_pressure_control',_'value':_'bp_control'}</t>
+          <t>blood_pressure_control</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Blood Pressure Control', 'value': 'bp_control'}</t>
+          <t>Blood Pressure Control</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'medication_management',_'value':_'med_mgmt'}</t>
+          <t>medication_management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Medication Management', 'value': 'med_mgmt'}</t>
+          <t>Medication Management</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'video_tutorials',_'value':_'video'}</t>
+          <t>video_tutorials</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Video Tutorials', 'value': 'video'}</t>
+          <t>Video Tutorials</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'interactive_webinars',_'value':_'webinars'}</t>
+          <t>interactive_webinars</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Interactive Webinars', 'value': 'webinars'}</t>
+          <t>Interactive Webinars</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'reading_material_(pdfs/blogs)',_'value':_'reading'}</t>
+          <t>reading_material_(pdfs/blogs)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Reading Material (PDFs/Blogs)', 'value': 'reading'}</t>
+          <t>Reading Material (PDFs/Blogs)</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'in-person_workshops',_'value':_'workshops'}</t>
+          <t>in-person_workshops</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'In-person Workshops', 'value': 'workshops'}</t>
+          <t>In-person Workshops</t>
         </is>
       </c>
     </row>
